--- a/output/일매출관리시스템_템플릿.xlsx
+++ b/output/일매출관리시스템_템플릿.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="stores" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="sales_logs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="monthly_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="missing_check" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사용예시_가이드" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="stores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="sales_logs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="monthly_summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="missing_check" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,10 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +39,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="4">
@@ -68,17 +75,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -501,6 +511,199 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="95" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>■ 이 파일에는 이미 예시(테스트) 데이터가 들어가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  sales_logs 탭 2~5행: S001 6/1 영업 90만원, S001 6/2 휴무, S001 6/1 영업 95만원(중복), S003 6/1 영업 65만원</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>■ Google Sheets로 열면 자동으로 계산되어야 하는 값 (monthly_summary, C1=2026/E1=6 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  S001 행: 월매출 900,000 / 영업일수 1 / 휴무일수 1 / 일평균 900,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           K열(1일)="중복확인"(빨간 배경) / L열(2일)="휴무"(회색 배경)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           나머지 입력 안 한 날짜 = "미입력"(노란 배경), 6월에 없는 날(31일) = "---"</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  S003 행: 월매출 650,000 / 영업일수 1 / K열(1일)=650000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  S002, S004~S018 행: 입력 데이터 없음 → 모든 날짜 "미입력", 월매출 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>■ Google Sheets로 열면 자동으로 계산되어야 하는 값 (missing_check, B1=2026-06-01 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  오늘 제출 수(B2) = 2  (S001, S003가 6/1에 제출함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  미제출 수(D2) = 16  (active 매장 18개 - 2개)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A5 이하 목록: S002, S004~S018 (S001, S003 제외) 16개 매장이 자동으로 나열되어야 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>■ sales_logs 탭에서 직접 확인할 것</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3행(S001 6/1 95만원, 중복테스트): I열(중복여부) = TRUE, 배경 빨간색</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1행/2행(S001): I열 = FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4행(S003): I열 = FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>■ 만약 위 값과 다르게 나온다면</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1) C1/E1(기준연도/월)이 2026/6으로 되어 있는지, B1(missing_check)이 2026-06-01인지 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2) sales_logs C열(영업일)이 '날짜' 형식인지(텍스트로 들어가면 SUMIFS/COUNTIFS가 안 됨)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3) stores G열 상태가 정확히 소문자 'active'인지 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4) missing_check A5가 #ERROR!면 apps_script/Code.gs의 refreshMissingCheck()로 대체</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>■ 실제 매출 데이터가 들어오면</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  이 4줄의 예시 데이터(sales_logs 2~5행)는 지우고 실제 Form 응답으로 채워야 합니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -511,46 +714,46 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>store_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>담당컨설턴트</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>업체명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>점주명</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>연락처</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>지역</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>입력링크</t>
         </is>
@@ -584,7 +787,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -614,7 +821,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -644,7 +855,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -674,7 +889,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -704,7 +923,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -734,7 +957,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -764,7 +991,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -794,7 +1025,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -824,7 +1059,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -854,7 +1093,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -884,7 +1127,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -914,7 +1161,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -944,7 +1195,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -974,7 +1229,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1004,7 +1263,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1034,7 +1297,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1064,7 +1331,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1094,7 +1365,11 @@
           <t>active</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(예시-형식만) https://docs.google.com/forms/d/e/FORM_ID/viewform?usp=pp_url&amp;entry.123456789=S018</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1106,13 +1381,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1129,63 +1404,87 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>제출시간</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>store_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>영업일</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>영업여부</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>일매출</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>log_id</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>업체명</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>중복여부</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>확인여부</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>수정메모</t>
         </is>
       </c>
     </row>
     <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>46174.91666666666</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>영업</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>900000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>테스트1: 정상 입력</t>
+        </is>
+      </c>
       <c r="G2">
         <f>ARRAYFORMULA(IF(A2:A="","","L"&amp;TEXT(ROW(A2:A)-1,"0000")))</f>
         <v/>
@@ -1199,6 +1498,93 @@
         <v/>
       </c>
       <c r="J2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>46175.91666666666</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>46175</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>휴무</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>테스트2: 휴무</t>
+        </is>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>46176.91666666666</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>영업</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>950000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>테스트3: 중복 입력(6/1 재입력)</t>
+        </is>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46174.89583333334</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>영업</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>650000</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>예시: 다른 매장 정상 입력</t>
+        </is>
+      </c>
+      <c r="J5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1225,7 +1611,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1278,165 +1664,165 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>기준연도</t>
         </is>
       </c>
-      <c r="C1" s="3" t="n">
+      <c r="C1" s="6" t="n">
         <v>2026</v>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>기준월</t>
         </is>
       </c>
-      <c r="E1" s="3" t="n">
+      <c r="E1" s="6" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>store_id</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>담당컨설턴트</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>업체명</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>입력률</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>미입력일수</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>휴무일수</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>영업일수</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>월매출</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>일평균</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>전월대비</t>
         </is>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="K3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="M3" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N3" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="P3" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="Q3" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="R3" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="S3" s="4" t="n">
+      <c r="S3" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="T3" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="V3" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="W3" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="X3" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="Y3" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="Z3" s="4" t="n">
+      <c r="Z3" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AA3" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="AB3" s="4" t="n">
+      <c r="AB3" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AC3" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="AD3" s="4" t="n">
+      <c r="AD3" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="AE3" s="4" t="n">
+      <c r="AE3" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="AF3" s="4" t="n">
+      <c r="AF3" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="AG3" s="4" t="n">
+      <c r="AG3" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="AH3" s="4" t="n">
+      <c r="AH3" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="AI3" s="4" t="n">
+      <c r="AI3" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="AJ3" s="4" t="n">
+      <c r="AJ3" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="AK3" s="4" t="n">
+      <c r="AK3" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="AL3" s="4" t="n">
+      <c r="AL3" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="AM3" s="4" t="n">
+      <c r="AM3" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="AN3" s="4" t="n">
+      <c r="AN3" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="AO3" s="4" t="n">
+      <c r="AO3" s="7" t="n">
         <v>31</v>
       </c>
     </row>
@@ -4460,7 +4846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4478,18 +4864,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>확인일</t>
         </is>
       </c>
-      <c r="B1" s="5">
-        <f>TODAY()</f>
-        <v/>
+      <c r="B1" s="8" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>오늘 제출 수</t>
         </is>
@@ -4498,7 +4883,7 @@
         <f>COUNTIF(sales_logs!$C$2:$C$1000,$B$1)</f>
         <v/>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>미제출 수</t>
         </is>
@@ -4507,7 +4892,7 @@
         <f>COUNTIF(stores!$G$2:$G$200,"active")-COUNTIF(sales_logs!$C$2:$C$1000,$B$1)</f>
         <v/>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>오늘 매출합</t>
         </is>
@@ -4518,32 +4903,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>담당컨설턴트</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>업체명</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>연락처</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>미입력일</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>입력링크</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
